--- a/マンダラート.xlsx
+++ b/マンダラート.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\okamoto masaki\Desktop\授業資料\2021_2Dプログラミング授業資料（Bパート）\8、工程管理・企画\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KOBEDENSHI\Desktop\返却時削除\3D制作\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A410C9B-41D6-49B1-9A4B-0568AC57DB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B821E614-031D-44C1-9B2F-E032CD341B37}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F58BB491-C7C8-497C-8B68-0A40878B3EF5}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8964" activeTab="1" xr2:uid="{F58BB491-C7C8-497C-8B68-0A40878B3EF5}"/>
   </bookViews>
   <sheets>
     <sheet name="手順・注意点" sheetId="1" r:id="rId1"/>
@@ -21,22 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>２、票の真ん中にコンセプト（目標を書く）</t>
     <rPh sb="2" eb="3">
@@ -154,6 +144,247 @@
     <t>マンダラート手順</t>
     <rPh sb="6" eb="8">
       <t>テジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>盗む</t>
+    <rPh sb="0" eb="1">
+      <t>ヌス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宝石</t>
+    <rPh sb="0" eb="2">
+      <t>ホウセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>家電</t>
+    <rPh sb="0" eb="2">
+      <t>カデン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>絵画</t>
+    <rPh sb="0" eb="2">
+      <t>カイガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>家の中</t>
+    <rPh sb="0" eb="1">
+      <t>イエ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ペット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金目の物</t>
+    <rPh sb="0" eb="2">
+      <t>カネメ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>隠密</t>
+    <rPh sb="0" eb="2">
+      <t>オンミツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>しゃがむ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>隠れる</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背後にそっと</t>
+    <rPh sb="0" eb="2">
+      <t>ハイゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自転車のサドル</t>
+    <rPh sb="0" eb="3">
+      <t>ジテンシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>物を投げて注意を惹く</t>
+    <rPh sb="0" eb="1">
+      <t>モノ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ナ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>チュウイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壁にそっと</t>
+    <rPh sb="0" eb="1">
+      <t>カベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>非殺生</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>セッショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>気絶</t>
+    <rPh sb="0" eb="2">
+      <t>キゼツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>睡眠</t>
+    <rPh sb="0" eb="2">
+      <t>スイミン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮死</t>
+    <rPh sb="0" eb="2">
+      <t>カシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>住人不在の家</t>
+    <rPh sb="0" eb="4">
+      <t>ジュウニンフザイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>イエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>別荘</t>
+    <rPh sb="0" eb="2">
+      <t>ベッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>豪邸</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>住居</t>
+    <rPh sb="0" eb="2">
+      <t>ジュウキョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>営業時間外のお店</t>
+    <rPh sb="0" eb="5">
+      <t>エイギョウジカンガイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ミセ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>小屋</t>
+    <rPh sb="0" eb="2">
+      <t>コヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ガレージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>倉庫</t>
+    <rPh sb="0" eb="2">
+      <t>ソウコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>道具</t>
+    <rPh sb="0" eb="2">
+      <t>ドウグ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ピッキングツール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>懐中電灯</t>
+    <rPh sb="0" eb="4">
+      <t>カイチュウデントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>盗品を入れるバッグ</t>
+    <rPh sb="0" eb="2">
+      <t>トウヒン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステルスアクション
+(泥棒)</t>
+    <rPh sb="11" eb="13">
+      <t>ドロボウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -314,7 +545,16 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -323,17 +563,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -650,29 +881,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D01C416-E986-444A-88D0-8DF65C381EBC}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="42.125" customWidth="1"/>
+    <col min="1" max="1" width="42.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A2" s="12" t="s">
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="6"/>
@@ -685,7 +916,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -699,7 +930,7 @@
       <c r="J3" s="8"/>
       <c r="K3" s="6"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -713,8 +944,8 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A5" s="10" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="6"/>
@@ -727,7 +958,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -741,8 +972,8 @@
       <c r="J6" s="8"/>
       <c r="K6" s="6"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A7" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="6"/>
@@ -755,8 +986,8 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A8" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="6"/>
@@ -769,7 +1000,7 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="C9" s="6"/>
       <c r="D9" s="8"/>
       <c r="E9" s="6"/>
@@ -780,7 +1011,7 @@
       <c r="J9" s="8"/>
       <c r="K9" s="6"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -797,41 +1028,62 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7EEDE6E-82BB-4470-845E-A63E03DC3AFD}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="9" width="20.625" customWidth="1"/>
+    <col min="1" max="9" width="20.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+    <row r="1" spans="1:9" ht="54.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="4"/>
-      <c r="B2" s="3">
+    <row r="2" spans="1:9" ht="54.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3" t="str">
         <f>D4</f>
-        <v>0</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3">
+        <v>盗む</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="3" t="str">
         <f>E4</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="2"/>
+        <v>ステージ</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="G2" s="4"/>
       <c r="H2" s="3">
         <f>F4</f>
@@ -839,37 +1091,61 @@
       </c>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
+    <row r="3" spans="1:9" ht="54.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="C3" s="4"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+    <row r="4" spans="1:9" ht="54.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="F4" s="3"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3">
+    <row r="5" spans="1:9" ht="54.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="3" t="str">
         <f>D5</f>
-        <v>0</v>
+        <v>隠密</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="9"/>
+      <c r="D5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>41</v>
+      </c>
       <c r="F5" s="3"/>
       <c r="G5" s="2"/>
       <c r="H5" s="3">
@@ -878,39 +1154,57 @@
       </c>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
+    <row r="6" spans="1:9" ht="54.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="F6" s="3"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4"/>
+    <row r="7" spans="1:9" ht="54.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4"/>
-      <c r="B8" s="3">
+    <row r="8" spans="1:9" ht="54.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="3" t="str">
         <f>D6</f>
-        <v>0</v>
+        <v>非殺生</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="3">
+      <c r="D8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="3" t="str">
         <f>E6</f>
-        <v>0</v>
+        <v>道具</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="4"/>
@@ -920,11 +1214,15 @@
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4"/>
+    <row r="9" spans="1:9" ht="54.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="4"/>
@@ -934,5 +1232,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>